--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,6 +513,51 @@
         <v>10699</v>
       </c>
       <c r="K2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>15:56:41</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>320.31</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-19.49</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>593.8 Hz | 921.9 Hz | 1257.8 Hz</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>2522</v>
+      </c>
+      <c r="J3" t="n">
+        <v>10409</v>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,6 +558,51 @@
         <v>10409</v>
       </c>
       <c r="K3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>16:01:01</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>351.56</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-22.57</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>671.9 Hz | 1007.8 Hz | 1414.1 Hz</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>2546</v>
+      </c>
+      <c r="J4" t="n">
+        <v>10326</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,6 +603,51 @@
         <v>10326</v>
       </c>
       <c r="K4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>16:01:52</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>484.38</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>968.8 Hz | 1453.1 Hz | 1945.3 Hz</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2506</v>
+      </c>
+      <c r="J5" t="n">
+        <v>58</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,6 +648,51 @@
         <v>58</v>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>16:03:20</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>484.38</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-12.16</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>968.8 Hz | 1453.1 Hz | 1945.3 Hz</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2549</v>
+      </c>
+      <c r="J6" t="n">
+        <v>11993</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,6 +693,51 @@
         <v>11993</v>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>16:03:38</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>484.38</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-11.35</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>968.8 Hz | 1453.1 Hz | 1945.3 Hz</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2555</v>
+      </c>
+      <c r="J7" t="n">
+        <v>61</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -738,6 +738,51 @@
         <v>61</v>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>16:04:06</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>484.38</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-9.390000000000001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>976.6 Hz | 1453.1 Hz | 1945.3 Hz</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2555</v>
+      </c>
+      <c r="J8" t="n">
+        <v>60</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,6 +783,51 @@
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>16:10:35</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>484.38</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-10.94</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>968.8 Hz | 1453.1 Hz | 1945.3 Hz</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2539</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10572</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,6 +833,51 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16:11:29</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>304.69</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-29.87</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>562.5 Hz | 867.2 Hz | 1203.1 Hz</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2522</v>
+      </c>
+      <c r="J10" t="n">
+        <v>57</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,6 +878,51 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>16:11:52</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>484.38</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-12.12</v>
+      </c>
+      <c r="G11" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>968.8 Hz | 1453.1 Hz | 1937.5 Hz</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2496</v>
+      </c>
+      <c r="J11" t="n">
+        <v>11222</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>🚨 SÍ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,6 +923,51 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>16:12:38</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>484.38</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-13.04</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>968.8 Hz | 1453.1 Hz | 1937.5 Hz</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2557</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10410</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -968,6 +968,51 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>16:13:13</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>484.38</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-11.86</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>968.8 Hz | 1453.1 Hz | 1945.3 Hz</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2499</v>
+      </c>
+      <c r="J13" t="n">
+        <v>11681</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,6 +1013,51 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>16:13:56</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>484.38</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-10.33</v>
+      </c>
+      <c r="G14" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>968.8 Hz | 1453.1 Hz | 1945.3 Hz</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2519</v>
+      </c>
+      <c r="J14" t="n">
+        <v>12046</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1058,6 +1058,51 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>16:14:29</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>484.38</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-11.36</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>968.8 Hz | 1453.1 Hz | 1945.3 Hz</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2499</v>
+      </c>
+      <c r="J15" t="n">
+        <v>61</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1103,6 +1103,51 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16:15:21</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>554.6900000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-12.51</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1109.4 Hz | 1664.1 Hz | 2234.4 Hz</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2545</v>
+      </c>
+      <c r="J16" t="n">
+        <v>10754</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1148,6 +1148,51 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>16:15:46</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>554.6900000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>76.04000000000001</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1109.4 Hz | 1671.9 Hz | 2226.6 Hz</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2536</v>
+      </c>
+      <c r="J17" t="n">
+        <v>57</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>🚨 SÍ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1193,6 +1193,51 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>16:17:30</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1437.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-4.15</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2835.9 Hz | 4273.4 Hz | 5726.6 Hz</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2504</v>
+      </c>
+      <c r="J18" t="n">
+        <v>11347</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1238,6 +1238,51 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>16:23:38</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1726.56</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-11.66</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>3406.2 Hz | 5218.8 Hz | 6859.4 Hz</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2521</v>
+      </c>
+      <c r="J19" t="n">
+        <v>10672</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1283,6 +1283,51 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>16:32:47</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>312.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-22.3</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>585.9 Hz | 953.1 Hz | 1226.6 Hz</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2526</v>
+      </c>
+      <c r="J20" t="n">
+        <v>18858</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1328,6 +1328,51 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>16:33:23</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>359.38</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-20.9</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>679.7 Hz | 1109.4 Hz | 1476.6 Hz</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2528</v>
+      </c>
+      <c r="J21" t="n">
+        <v>69</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1373,6 +1373,51 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>16:33:56</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1257.81</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-4.36</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2476.6 Hz | 3796.9 Hz | 5039.1 Hz</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2561</v>
+      </c>
+      <c r="J22" t="n">
+        <v>69</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1418,6 +1418,51 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16:34:28</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1289.06</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-4.58</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2578.1 Hz | 3851.6 Hz | 5187.5 Hz</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2556</v>
+      </c>
+      <c r="J23" t="n">
+        <v>10576</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1463,6 +1463,51 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16:36:12</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>312.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-23.09</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>585.9 Hz | 914.1 Hz | 1218.8 Hz</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>2520</v>
+      </c>
+      <c r="J24" t="n">
+        <v>21254</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1508,6 +1508,51 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>16:36:53</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>320.31</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-13.69</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>601.6 Hz | 914.1 Hz | 1257.8 Hz</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>2555</v>
+      </c>
+      <c r="J25" t="n">
+        <v>65</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1553,6 +1553,51 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>16:37:22</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>320.31</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-20.88</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>664.1 Hz | 921.9 Hz | 1250.0 Hz</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>2516</v>
+      </c>
+      <c r="J26" t="n">
+        <v>66</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1598,6 +1598,51 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>16:37:36</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>328.12</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-22.23</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>648.4 Hz | 968.8 Hz | 1359.4 Hz</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2506</v>
+      </c>
+      <c r="J27" t="n">
+        <v>82</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-06-04.xlsx
+++ b/datos/excel/reporte_2026-06-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1643,6 +1643,51 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>16:38:28</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-14.21</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>937.5 Hz | 1398.4 Hz | 1867.2 Hz</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>2549</v>
+      </c>
+      <c r="J28" t="n">
+        <v>11607</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
